--- a/Intersecciones/excels/AREQUIPA-CAMANA-CAMANA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-CAMANA-CAMANA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,6 +579,58 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>040201</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I-186375</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>040208</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CAMANA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SAMUEL PASTOR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-16.6136775</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-72.7057091</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Avenida 3 de Noviembre / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>040201</t>
         </is>
